--- a/analysis/data/annotation/[Archived] Labeling SDG 12 - Benchmarking Dataset.xlsx
+++ b/analysis/data/annotation/[Archived] Labeling SDG 12 - Benchmarking Dataset.xlsx
@@ -20466,7 +20466,7 @@
     <row r="2">
       <c r="A2" s="24" t="str">
         <f t="shared" ref="A2:A81" si="1">LEFT(MD5(B2), 7)</f>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>143</v>
@@ -20488,7 +20488,7 @@
     <row r="3">
       <c r="A3" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>187</v>
@@ -20510,7 +20510,7 @@
     <row r="4">
       <c r="A4" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>201</v>
@@ -20532,7 +20532,7 @@
     <row r="5">
       <c r="A5" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>152</v>
@@ -20554,7 +20554,7 @@
     <row r="6">
       <c r="A6" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>160</v>
@@ -20576,7 +20576,7 @@
     <row r="7">
       <c r="A7" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B7" s="55" t="s">
         <v>484</v>
@@ -20601,7 +20601,7 @@
     <row r="8">
       <c r="A8" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>248</v>
@@ -20623,7 +20623,7 @@
     <row r="9">
       <c r="A9" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>166</v>
@@ -20645,7 +20645,7 @@
     <row r="10">
       <c r="A10" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>298</v>
@@ -20667,7 +20667,7 @@
     <row r="11">
       <c r="A11" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>191</v>
@@ -20689,7 +20689,7 @@
     <row r="12">
       <c r="A12" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>113</v>
@@ -20711,7 +20711,7 @@
     <row r="13">
       <c r="A13" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>250</v>
@@ -20733,7 +20733,7 @@
     <row r="14">
       <c r="A14" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>128</v>
@@ -20755,7 +20755,7 @@
     <row r="15">
       <c r="A15" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>141</v>
@@ -20777,7 +20777,7 @@
     <row r="16">
       <c r="A16" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>106</v>
@@ -20799,7 +20799,7 @@
     <row r="17">
       <c r="A17" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>213</v>
@@ -20821,7 +20821,7 @@
     <row r="18">
       <c r="A18" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>292</v>
@@ -20843,7 +20843,7 @@
     <row r="19">
       <c r="A19" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>211</v>
@@ -20865,7 +20865,7 @@
     <row r="20">
       <c r="A20" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B20" s="55" t="s">
         <v>486</v>
@@ -20890,7 +20890,7 @@
     <row r="21">
       <c r="A21" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B21" s="55" t="s">
         <v>488</v>
@@ -20915,7 +20915,7 @@
     <row r="22">
       <c r="A22" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>217</v>
@@ -20937,7 +20937,7 @@
     <row r="23">
       <c r="A23" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>205</v>
@@ -20959,7 +20959,7 @@
     <row r="24">
       <c r="A24" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>256</v>
@@ -20981,7 +20981,7 @@
     <row r="25">
       <c r="A25" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>224</v>
@@ -21003,7 +21003,7 @@
     <row r="26">
       <c r="A26" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>238</v>
@@ -21025,7 +21025,7 @@
     <row r="27">
       <c r="A27" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>158</v>
@@ -21047,7 +21047,7 @@
     <row r="28">
       <c r="A28" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>199</v>
@@ -21069,7 +21069,7 @@
     <row r="29">
       <c r="A29" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>286</v>
@@ -21091,7 +21091,7 @@
     <row r="30">
       <c r="A30" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>262</v>
@@ -21113,7 +21113,7 @@
     <row r="31">
       <c r="A31" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B31" s="55" t="s">
         <v>490</v>
@@ -21138,7 +21138,7 @@
     <row r="32">
       <c r="A32" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>282</v>
@@ -21160,7 +21160,7 @@
     <row r="33">
       <c r="A33" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>172</v>
@@ -21185,7 +21185,7 @@
     <row r="34">
       <c r="A34" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>126</v>
@@ -21207,7 +21207,7 @@
     <row r="35">
       <c r="A35" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>230</v>
@@ -21229,7 +21229,7 @@
     <row r="36">
       <c r="A36" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>178</v>
@@ -21251,7 +21251,7 @@
     <row r="37">
       <c r="A37" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>168</v>
@@ -21273,7 +21273,7 @@
     <row r="38">
       <c r="A38" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>189</v>
@@ -21295,7 +21295,7 @@
     <row r="39">
       <c r="A39" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>232</v>
@@ -21317,7 +21317,7 @@
     <row r="40">
       <c r="A40" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>109</v>
@@ -21339,7 +21339,7 @@
     <row r="41">
       <c r="A41" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>197</v>
@@ -21364,7 +21364,7 @@
     <row r="42">
       <c r="A42" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>193</v>
@@ -21386,7 +21386,7 @@
     <row r="43">
       <c r="A43" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>252</v>
@@ -21408,7 +21408,7 @@
     <row r="44">
       <c r="A44" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>284</v>
@@ -21433,7 +21433,7 @@
     <row r="45">
       <c r="A45" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>220</v>
@@ -21455,7 +21455,7 @@
     <row r="46">
       <c r="A46" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>280</v>
@@ -21477,7 +21477,7 @@
     <row r="47">
       <c r="A47" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B47" s="55" t="s">
         <v>491</v>
@@ -21502,7 +21502,7 @@
     <row r="48">
       <c r="A48" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>300</v>
@@ -21524,7 +21524,7 @@
     <row r="49">
       <c r="A49" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>101</v>
@@ -21546,7 +21546,7 @@
     <row r="50">
       <c r="A50" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>258</v>
@@ -21568,7 +21568,7 @@
     <row r="51">
       <c r="A51" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>145</v>
@@ -21590,7 +21590,7 @@
     <row r="52">
       <c r="A52" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>164</v>
@@ -21612,7 +21612,7 @@
     <row r="53">
       <c r="A53" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B53" s="12" t="s">
         <v>276</v>
@@ -21634,7 +21634,7 @@
     <row r="54">
       <c r="A54" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>228</v>
@@ -21656,7 +21656,7 @@
     <row r="55">
       <c r="A55" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B55" s="12" t="s">
         <v>95</v>
@@ -21678,7 +21678,7 @@
     <row r="56">
       <c r="A56" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>134</v>
@@ -21700,7 +21700,7 @@
     <row r="57">
       <c r="A57" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B57" s="12" t="s">
         <v>117</v>
@@ -21722,7 +21722,7 @@
     <row r="58">
       <c r="A58" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>195</v>
@@ -21744,7 +21744,7 @@
     <row r="59">
       <c r="A59" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>266</v>
@@ -21766,7 +21766,7 @@
     <row r="60">
       <c r="A60" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>115</v>
@@ -21791,7 +21791,7 @@
     <row r="61">
       <c r="A61" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B61" s="12" t="s">
         <v>119</v>
@@ -21813,7 +21813,7 @@
     <row r="62">
       <c r="A62" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>132</v>
@@ -21835,7 +21835,7 @@
     <row r="63">
       <c r="A63" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B63" s="55" t="s">
         <v>493</v>
@@ -21860,7 +21860,7 @@
     <row r="64">
       <c r="A64" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>148</v>
@@ -21882,7 +21882,7 @@
     <row r="65">
       <c r="A65" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B65" s="12" t="s">
         <v>268</v>
@@ -21904,7 +21904,7 @@
     <row r="66">
       <c r="A66" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>185</v>
@@ -21926,7 +21926,7 @@
     <row r="67">
       <c r="A67" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B67" s="12" t="s">
         <v>121</v>
@@ -21948,7 +21948,7 @@
     <row r="68">
       <c r="A68" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>254</v>
@@ -21970,7 +21970,7 @@
     <row r="69">
       <c r="A69" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>130</v>
@@ -21992,7 +21992,7 @@
     <row r="70">
       <c r="A70" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>180</v>
@@ -22014,7 +22014,7 @@
     <row r="71">
       <c r="A71" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B71" s="12" t="s">
         <v>294</v>
@@ -22036,7 +22036,7 @@
     <row r="72">
       <c r="A72" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>260</v>
@@ -22058,7 +22058,7 @@
     <row r="73">
       <c r="A73" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B73" s="12" t="s">
         <v>139</v>
@@ -22080,7 +22080,7 @@
     <row r="74">
       <c r="A74" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>176</v>
@@ -22102,7 +22102,7 @@
     <row r="75">
       <c r="A75" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B75" s="12" t="s">
         <v>270</v>
@@ -22124,7 +22124,7 @@
     <row r="76">
       <c r="A76" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>162</v>
@@ -22146,7 +22146,7 @@
     <row r="77">
       <c r="A77" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B77" s="55" t="s">
         <v>494</v>
@@ -22171,7 +22171,7 @@
     <row r="78">
       <c r="A78" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>264</v>
@@ -22193,7 +22193,7 @@
     <row r="79">
       <c r="A79" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B79" s="12" t="s">
         <v>246</v>
@@ -22218,7 +22218,7 @@
     <row r="80">
       <c r="A80" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>203</v>
@@ -22240,7 +22240,7 @@
     <row r="81">
       <c r="A81" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B81" s="12" t="s">
         <v>296</v>
